--- a/public/olo_exp.xlsx
+++ b/public/olo_exp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2293b72959587e28/PAYT_ANALYSIS/model/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{D30D7030-3FA5-FC45-89E7-75268989D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01D90DE3-71AC-EE4C-9FA7-24BE56C3433A}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{D30D7030-3FA5-FC45-89E7-75268989D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E25FB69-B7B6-7245-A531-2ECFD050CDD7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="41120" windowHeight="23980" xr2:uid="{E219D4B1-7D27-470C-93D5-D94F3CBAEDA8}"/>
+    <workbookView xWindow="17720" yWindow="800" windowWidth="23400" windowHeight="23980" xr2:uid="{E219D4B1-7D27-470C-93D5-D94F3CBAEDA8}"/>
   </bookViews>
   <sheets>
     <sheet name="N HMBA 2025-2030 odhad" sheetId="1" r:id="rId1"/>
@@ -72,69 +72,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Cestovné</t>
-  </si>
-  <si>
-    <t>Dane</t>
-  </si>
-  <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>Finančné náklady</t>
-  </si>
-  <si>
-    <t>Informačné technológie</t>
-  </si>
-  <si>
-    <t>Náklady na autá</t>
-  </si>
-  <si>
-    <t>Odpisy</t>
-  </si>
-  <si>
-    <t>Oprava a údržba</t>
-  </si>
-  <si>
-    <t>Osobné náklady</t>
-  </si>
-  <si>
-    <t>Ostatné prevádzkové náklady</t>
-  </si>
-  <si>
-    <t>Poistenie</t>
-  </si>
-  <si>
-    <t>Prenájom</t>
-  </si>
-  <si>
-    <t>Reklamné náklady</t>
-  </si>
-  <si>
-    <t>Služby</t>
-  </si>
-  <si>
-    <t>Spotreba kontajnerov</t>
-  </si>
-  <si>
-    <t>Spotreba materiálu</t>
-  </si>
-  <si>
-    <t>Stráženie a ochrana majetku</t>
-  </si>
-  <si>
-    <t>Telekomunikačné služby</t>
-  </si>
-  <si>
-    <t>Vnútropodnikové náklady</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>NakladyOLO</t>
   </si>
   <si>
     <t>Rok</t>
+  </si>
+  <si>
+    <t>Incineration</t>
+  </si>
+  <si>
+    <t>Residential waste collection</t>
+  </si>
+  <si>
+    <t>Green waste collection</t>
+  </si>
+  <si>
+    <t>Organic waste collection</t>
+  </si>
+  <si>
+    <t>Collection yards/points</t>
   </si>
 </sst>
 </file>
@@ -168,7 +126,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,12 +151,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -212,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -221,8 +173,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,502 +520,226 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C1" s="2">
         <v>2025</v>
       </c>
-      <c r="C1" s="2">
+      <c r="D1" s="2">
         <v>2026</v>
       </c>
-      <c r="D1" s="2">
+      <c r="E1" s="2">
         <v>2027</v>
       </c>
-      <c r="E1" s="2">
+      <c r="F1" s="2">
         <v>2028</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="2">
         <v>2029</v>
       </c>
-      <c r="G1" s="2">
+      <c r="H1" s="2">
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B2" s="4">
-        <f>SUM(B3:B21)</f>
+        <f>SUM(B3:B7)</f>
+        <v>28067934</v>
+      </c>
+      <c r="C2" s="4">
         <v>28366977.080905046</v>
       </c>
-      <c r="C2" s="4">
-        <f t="shared" ref="C2:G2" si="0">SUM(C3:C21)</f>
+      <c r="D2" s="4">
         <v>30099223.25836705</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4">
+        <v>30525195.955587134</v>
+      </c>
+      <c r="F2" s="4">
+        <v>31075825.854476817</v>
+      </c>
+      <c r="G2" s="4">
+        <v>31852721.500838734</v>
+      </c>
+      <c r="H2" s="4">
+        <v>32649039.53835969</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>9795084</v>
+      </c>
+      <c r="C3" s="6">
+        <f>B3*C$2/B$2</f>
+        <v>9899443.3766852859</v>
+      </c>
+      <c r="D3" s="6">
+        <f t="shared" ref="D3:H3" si="0">C3*D$2/C$2</f>
+        <v>10503958.722094011</v>
+      </c>
+      <c r="E3" s="6">
         <f t="shared" si="0"/>
-        <v>30525195.955587134</v>
-      </c>
-      <c r="E2" s="4">
+        <v>10652613.708634071</v>
+      </c>
+      <c r="F3" s="6">
         <f t="shared" si="0"/>
-        <v>31075825.854476817</v>
-      </c>
-      <c r="F2" s="4">
+        <v>10844771.282915667</v>
+      </c>
+      <c r="G3" s="6">
         <f t="shared" si="0"/>
-        <v>31852721.500838734</v>
-      </c>
-      <c r="G2" s="4">
+        <v>11115890.564988557</v>
+      </c>
+      <c r="H3" s="6">
         <f t="shared" si="0"/>
-        <v>32649039.53835969</v>
+        <v>11393787.829113267</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="6">
-        <v>21422.676420066397</v>
-      </c>
-      <c r="C3" s="6">
-        <v>22817.298256846829</v>
-      </c>
-      <c r="D3" s="6">
-        <v>23387.730713267996</v>
-      </c>
-      <c r="E3" s="6">
-        <v>23972.423981099695</v>
-      </c>
-      <c r="F3" s="6">
-        <v>24571.734580627184</v>
-      </c>
-      <c r="G3" s="6">
-        <v>25186.027945142861</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
+        <v>9332300</v>
+      </c>
+      <c r="C4" s="6">
+        <f t="shared" ref="C4:H7" si="1">B4*C$2/B$2</f>
+        <v>9431728.7553879153</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" si="1"/>
+        <v>10007682.831734562</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" si="1"/>
+        <v>10149314.381896643</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="1"/>
+        <v>10332393.17228457</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="1"/>
+        <v>10590703.001591682</v>
+      </c>
+      <c r="H4" s="6">
+        <f t="shared" si="1"/>
+        <v>10855470.576631472</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6">
-        <v>260315.36956375791</v>
-      </c>
-      <c r="C4" s="6">
-        <v>260315.36956375791</v>
-      </c>
-      <c r="D4" s="6">
-        <v>260315.36956375791</v>
-      </c>
-      <c r="E4" s="6">
-        <v>266823.25380285183</v>
-      </c>
-      <c r="F4" s="6">
-        <v>273493.83514792309</v>
-      </c>
-      <c r="G4" s="6">
-        <v>280331.18102662114</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6">
+        <v>2450000</v>
+      </c>
+      <c r="C5" s="6">
+        <f t="shared" si="1"/>
+        <v>2476102.9382574921</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" si="1"/>
+        <v>2627307.6238172459</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="1"/>
+        <v>2664490.0223574876</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="1"/>
+        <v>2712553.5261508101</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="1"/>
+        <v>2780367.3643045798</v>
+      </c>
+      <c r="H5" s="6">
+        <f t="shared" si="1"/>
+        <v>2849876.5484121931</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6">
-        <v>286120.282529502</v>
-      </c>
-      <c r="C5" s="6">
-        <v>304746.78774001158</v>
-      </c>
-      <c r="D5" s="6">
-        <v>312365.45743351185</v>
-      </c>
-      <c r="E5" s="6">
-        <v>320174.59386934963</v>
-      </c>
-      <c r="F5" s="6">
-        <v>328178.95871608332</v>
-      </c>
-      <c r="G5" s="6">
-        <v>336383.43268398539</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5598490</v>
+      </c>
+      <c r="C6" s="6">
+        <f t="shared" si="1"/>
+        <v>5658137.7709408924</v>
+      </c>
+      <c r="D6" s="6">
+        <f t="shared" si="1"/>
+        <v>6003655.2893324941</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="1"/>
+        <v>6088620.7123543555</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="1"/>
+        <v>6198450.5267836936</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="1"/>
+        <v>6353411.7899532849</v>
+      </c>
+      <c r="H6" s="6">
+        <f t="shared" si="1"/>
+        <v>6512247.0847021146</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6">
-        <v>7885.9621240121751</v>
-      </c>
-      <c r="C6" s="6">
-        <v>8399.3403203923972</v>
-      </c>
-      <c r="D6" s="6">
-        <v>8609.3238284022063</v>
-      </c>
-      <c r="E6" s="6">
-        <v>8824.5569241122612</v>
-      </c>
-      <c r="F6" s="6">
-        <v>9045.1708472150676</v>
-      </c>
-      <c r="G6" s="6">
-        <v>9271.3001183954439</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>755875.07794023503</v>
+        <v>892060</v>
       </c>
       <c r="C7" s="6">
-        <v>800000</v>
+        <f t="shared" si="1"/>
+        <v>901564.23963346065</v>
       </c>
       <c r="D7" s="6">
-        <v>500000</v>
+        <f t="shared" si="1"/>
+        <v>956618.79138873972</v>
       </c>
       <c r="E7" s="6">
-        <v>300000</v>
+        <f t="shared" si="1"/>
+        <v>970157.13034457981</v>
       </c>
       <c r="F7" s="6">
-        <v>307500</v>
+        <f t="shared" si="1"/>
+        <v>987657.34634207829</v>
       </c>
       <c r="G7" s="6">
-        <v>315187.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6">
-        <v>918252.04016480478</v>
-      </c>
-      <c r="C8" s="6">
-        <v>977451.69566748803</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1001887.9880591752</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1026935.1877606545</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1052608.5674546708</v>
-      </c>
-      <c r="G8" s="6">
-        <v>1078923.7816410374</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="6">
-        <v>2523069.3952114773</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2687321.872599334</v>
-      </c>
-      <c r="D9" s="6">
-        <v>2754504.9194143172</v>
-      </c>
-      <c r="E9" s="6">
-        <v>2823367.5423996751</v>
-      </c>
-      <c r="F9" s="6">
-        <v>2893951.7309596669</v>
-      </c>
-      <c r="G9" s="6">
-        <v>2966300.5242336583</v>
-      </c>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1673319.9361093289</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1784199.8598313855</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1828804.85632717</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1874524.9777353492</v>
-      </c>
-      <c r="F10" s="6">
-        <v>1921388.1021787329</v>
-      </c>
-      <c r="G10" s="6">
-        <v>1969422.8047332009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>14460337.623422351</v>
-      </c>
-      <c r="C11" s="6">
-        <v>15377302.714427851</v>
-      </c>
-      <c r="D11" s="6">
-        <v>15761735.282288546</v>
-      </c>
-      <c r="E11" s="6">
-        <v>16155778.664345758</v>
-      </c>
-      <c r="F11" s="6">
-        <v>16559673.1309544</v>
-      </c>
-      <c r="G11" s="6">
-        <v>16973664.959228259</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6">
-        <v>222970.97844063235</v>
-      </c>
-      <c r="C12" s="6">
-        <v>240204.13822131581</v>
-      </c>
-      <c r="D12" s="6">
-        <v>246209.24167684867</v>
-      </c>
-      <c r="E12" s="6">
-        <v>252364.47271876986</v>
-      </c>
-      <c r="F12" s="6">
-        <v>258673.58453673907</v>
-      </c>
-      <c r="G12" s="6">
-        <v>265140.42415015755</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="6">
-        <v>608970.04166820832</v>
-      </c>
-      <c r="C13" s="6">
-        <v>608970.04166820832</v>
-      </c>
-      <c r="D13" s="6">
-        <v>624194.29270991345</v>
-      </c>
-      <c r="E13" s="6">
-        <v>639799.15002766124</v>
-      </c>
-      <c r="F13" s="6">
-        <v>655794.12877835275</v>
-      </c>
-      <c r="G13" s="6">
-        <v>672188.98199781147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="6">
-        <v>142954.4777647476</v>
-      </c>
-      <c r="C14" s="6">
-        <v>152260.85164852219</v>
-      </c>
-      <c r="D14" s="6">
-        <v>156067.37293973524</v>
-      </c>
-      <c r="E14" s="6">
-        <v>159969.05726322861</v>
-      </c>
-      <c r="F14" s="6">
-        <v>163968.2836948093</v>
-      </c>
-      <c r="G14" s="6">
-        <v>168067.49078717953</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="6">
-        <v>88743.252532264814</v>
-      </c>
-      <c r="C15" s="6">
-        <v>94520.461477664794</v>
-      </c>
-      <c r="D15" s="6">
-        <v>96883.47301460641</v>
-      </c>
-      <c r="E15" s="6">
-        <v>99305.559839971567</v>
-      </c>
-      <c r="F15" s="6">
-        <v>101788.19883597085</v>
-      </c>
-      <c r="G15" s="6">
-        <v>104332.9038068701</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="6">
-        <v>3765766.0507633202</v>
-      </c>
-      <c r="C16" s="6">
-        <v>4015298.6377201197</v>
-      </c>
-      <c r="D16" s="6">
-        <v>4115681.1036631223</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4218573.1312547</v>
-      </c>
-      <c r="F16" s="6">
-        <v>4324037.4595360672</v>
-      </c>
-      <c r="G16" s="6">
-        <v>4432138.3960244684</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6">
-        <v>284027.55999999988</v>
-      </c>
-      <c r="C17" s="6">
-        <v>302517.8284266112</v>
-      </c>
-      <c r="D17" s="6">
-        <v>310080.77413727646</v>
-      </c>
-      <c r="E17" s="6">
-        <v>317832.79349070834</v>
-      </c>
-      <c r="F17" s="6">
-        <v>325778.61332797603</v>
-      </c>
-      <c r="G17" s="6">
-        <v>333923.07866117539</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="6">
-        <v>1154154.1119277945</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1229289.8464150468</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1260022.092575423</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1291522.6448898085</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1323810.7110120535</v>
-      </c>
-      <c r="G18" s="6">
-        <v>1356905.9787873547</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="6">
-        <v>179894.18081207399</v>
-      </c>
-      <c r="C19" s="6">
-        <v>191605.33902362431</v>
-      </c>
-      <c r="D19" s="6">
-        <v>196395.4724992149</v>
-      </c>
-      <c r="E19" s="6">
-        <v>201305.35931169524</v>
-      </c>
-      <c r="F19" s="6">
-        <v>206337.99329448759</v>
-      </c>
-      <c r="G19" s="6">
-        <v>211496.44312684977</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="6">
-        <v>94280.189706728939</v>
-      </c>
-      <c r="C20" s="6">
-        <v>100417.85471004501</v>
-      </c>
-      <c r="D20" s="6">
-        <v>102928.30107779613</v>
-      </c>
-      <c r="E20" s="6">
-        <v>105501.50860474103</v>
-      </c>
-      <c r="F20" s="6">
-        <v>108139.04631985954</v>
-      </c>
-      <c r="G20" s="6">
-        <v>110842.52247785602</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="6">
-        <v>918617.87380373513</v>
-      </c>
-      <c r="C21" s="6">
-        <v>941583.3206488284</v>
-      </c>
-      <c r="D21" s="6">
-        <v>965122.903665049</v>
-      </c>
-      <c r="E21" s="6">
-        <v>989250.97625667509</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1013982.2506630919</v>
-      </c>
-      <c r="G21" s="6">
-        <v>1039331.8069296691</v>
+        <f t="shared" si="1"/>
+        <v>1012348.7800006301</v>
+      </c>
+      <c r="H7" s="6">
+        <f t="shared" si="1"/>
+        <v>1037657.4995006454</v>
       </c>
     </row>
   </sheetData>

--- a/public/olo_exp.xlsx
+++ b/public/olo_exp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2293b72959587e28/PAYT_ANALYSIS/model/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{D30D7030-3FA5-FC45-89E7-75268989D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E25FB69-B7B6-7245-A531-2ECFD050CDD7}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{D30D7030-3FA5-FC45-89E7-75268989D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4EFF69A-07F3-9546-A5AB-CAAE614B043B}"/>
   <bookViews>
     <workbookView xWindow="17720" yWindow="800" windowWidth="23400" windowHeight="23980" xr2:uid="{E219D4B1-7D27-470C-93D5-D94F3CBAEDA8}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +120,14 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -161,10 +169,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -174,9 +183,11 @@
     <xf numFmtId="4" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -520,7 +531,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
@@ -529,7 +540,7 @@
     <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -555,7 +566,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -582,7 +593,7 @@
         <v>32649039.53835969</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -613,8 +624,12 @@
         <f t="shared" si="0"/>
         <v>11393787.829113267</v>
       </c>
+      <c r="I3" s="7">
+        <f>POWER(H3/B3,1/6)-1</f>
+        <v>2.5518093612853621E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -645,8 +660,12 @@
         <f t="shared" si="1"/>
         <v>10855470.576631472</v>
       </c>
+      <c r="I4" s="7">
+        <f>POWER(H4/B4,1/6)-1</f>
+        <v>2.5518093612853399E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -677,8 +696,12 @@
         <f t="shared" si="1"/>
         <v>2849876.5484121931</v>
       </c>
+      <c r="I5" s="7">
+        <f>POWER(H5/B5,1/6)-1</f>
+        <v>2.5518093612853621E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -709,8 +732,12 @@
         <f t="shared" si="1"/>
         <v>6512247.0847021146</v>
       </c>
+      <c r="I6" s="7">
+        <f>POWER(H6/B6,1/6)-1</f>
+        <v>2.5518093612853621E-2</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -740,6 +767,10 @@
       <c r="H7" s="6">
         <f t="shared" si="1"/>
         <v>1037657.4995006454</v>
+      </c>
+      <c r="I7" s="7">
+        <f>POWER(H7/B7,1/6)-1</f>
+        <v>2.5518093612853621E-2</v>
       </c>
     </row>
   </sheetData>

--- a/public/olo_exp.xlsx
+++ b/public/olo_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2293b72959587e28/PAYT_ANALYSIS/model/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{D30D7030-3FA5-FC45-89E7-75268989D8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4EFF69A-07F3-9546-A5AB-CAAE614B043B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A40B2E6A-FEF6-3245-8A0A-28F88976B576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17720" yWindow="800" windowWidth="23400" windowHeight="23980" xr2:uid="{E219D4B1-7D27-470C-93D5-D94F3CBAEDA8}"/>
   </bookViews>
@@ -52,6 +52,7 @@
     <definedName name="y">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -624,10 +625,7 @@
         <f t="shared" si="0"/>
         <v>11393787.829113267</v>
       </c>
-      <c r="I3" s="7">
-        <f>POWER(H3/B3,1/6)-1</f>
-        <v>2.5518093612853621E-2</v>
-      </c>
+      <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
@@ -660,10 +658,7 @@
         <f t="shared" si="1"/>
         <v>10855470.576631472</v>
       </c>
-      <c r="I4" s="7">
-        <f>POWER(H4/B4,1/6)-1</f>
-        <v>2.5518093612853399E-2</v>
-      </c>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -696,10 +691,7 @@
         <f t="shared" si="1"/>
         <v>2849876.5484121931</v>
       </c>
-      <c r="I5" s="7">
-        <f>POWER(H5/B5,1/6)-1</f>
-        <v>2.5518093612853621E-2</v>
-      </c>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
@@ -732,10 +724,7 @@
         <f t="shared" si="1"/>
         <v>6512247.0847021146</v>
       </c>
-      <c r="I6" s="7">
-        <f>POWER(H6/B6,1/6)-1</f>
-        <v>2.5518093612853621E-2</v>
-      </c>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -768,10 +757,7 @@
         <f t="shared" si="1"/>
         <v>1037657.4995006454</v>
       </c>
-      <c r="I7" s="7">
-        <f>POWER(H7/B7,1/6)-1</f>
-        <v>2.5518093612853621E-2</v>
-      </c>
+      <c r="I7" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
